--- a/data/Brienz (BE)/cost/cost_report.xlsx
+++ b/data/Brienz (BE)/cost/cost_report.xlsx
@@ -482,22 +482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>728.9470550847611</v>
+        <v>622.1340021290127</v>
       </c>
       <c r="C2" t="n">
-        <v>19060.82015283921</v>
+        <v>19349.76981795164</v>
       </c>
       <c r="D2" t="n">
-        <v>14394.11998582338</v>
+        <v>15158.65936252239</v>
       </c>
       <c r="E2" t="n">
-        <v>4253.999182212385</v>
+        <v>4423.970288040319</v>
       </c>
       <c r="F2" t="n">
-        <v>39688.91160986795</v>
+        <v>39536.84464478992</v>
       </c>
       <c r="G2" t="n">
-        <v>78126.79798582768</v>
+        <v>79091.37811543328</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.1213301515629296</v>
+        <v>0.1228281350505016</v>
       </c>
     </row>
     <row r="3">
@@ -515,30 +515,30 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>735.0885808519429</v>
+        <v>625.3252779986253</v>
       </c>
       <c r="C3" t="n">
-        <v>18992.86970480766</v>
+        <v>13164.03996169887</v>
       </c>
       <c r="D3" t="n">
-        <v>15018.81648338679</v>
+        <v>53964.49989928913</v>
       </c>
       <c r="E3" t="n">
-        <v>4438.688712355585</v>
+        <v>2407.269428458511</v>
       </c>
       <c r="F3" t="n">
-        <v>41458.71643227667</v>
+        <v>25347.04544940988</v>
       </c>
       <c r="G3" t="n">
-        <v>80644.17991367864</v>
+        <v>95508.18001685503</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>cp_dr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.1252396210243985</v>
+        <v>0.1483232675047897</v>
       </c>
     </row>
     <row r="4">
@@ -548,30 +548,30 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>738.2319178164894</v>
+        <v>624.8532860198999</v>
       </c>
       <c r="C4" t="n">
-        <v>13299.35940917076</v>
+        <v>13231.07390913184</v>
       </c>
       <c r="D4" t="n">
-        <v>49897.86515585941</v>
+        <v>53317.37147089486</v>
       </c>
       <c r="E4" t="n">
-        <v>3991.59748862071</v>
+        <v>2240.996671183357</v>
       </c>
       <c r="F4" t="n">
-        <v>26778.20023327113</v>
+        <v>23630.6453292277</v>
       </c>
       <c r="G4" t="n">
-        <v>94705.25420473851</v>
+        <v>93044.94066645767</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cp_cu</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.1470763315879285</v>
+        <v>0.144497880935463</v>
       </c>
     </row>
     <row r="5">
@@ -581,30 +581,30 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>734.4283932842882</v>
+        <v>624.1439186058343</v>
       </c>
       <c r="C5" t="n">
-        <v>13364.0339105916</v>
+        <v>19201.00849466657</v>
       </c>
       <c r="D5" t="n">
-        <v>49377.54938786665</v>
+        <v>16691.34602866002</v>
       </c>
       <c r="E5" t="n">
-        <v>3913.659692784379</v>
+        <v>4170.021040778571</v>
       </c>
       <c r="F5" t="n">
-        <v>24805.667966195</v>
+        <v>41075.08361035249</v>
       </c>
       <c r="G5" t="n">
-        <v>92195.33935072192</v>
+        <v>81761.60309306349</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cp_cu</t>
+          <t>cp_dr</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.1431784584189408</v>
+        <v>0.1269749682702857</v>
       </c>
     </row>
   </sheetData>
